--- a/results/Int Task Remove ACC -0.5/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.5/Linea_fi_all.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.025825362542425158 +/- 0.0034690589877476984</t>
+          <t>0.025825362542425158 +/- 0.0034081498570322976</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -906,77 +906,77 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.000154273372415914 +/- 0.0014684361659106201</t>
+          <t>-0.00018512804689909678 +/- 0.0014219955102502848</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>-0.0003702560937982158 +/- 0.0011853978841282684</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.060783708731872874 +/- 0.006957027818014815</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.018111693921629125 +/- 0.003601019436102377</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.018111693921629125 +/- 0.003601019436102377</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-0.014686825053995678 +/- 0.0035049606470010193</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.023295279234804057 +/- 0.0037390213447702925</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.02974390620178957 +/- 0.0043178909434213805</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.0374884294970688 +/- 0.003532152790502694</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.03853748842949707 +/- 0.0026522459947968713</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.02162912681271213 +/- 0.004585735447845404</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.2662141314409133 +/- 0.008043311212818587</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.0013884603517432814 +/- 0.002633514700817101</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.11289725393397101 +/- 0.008174392680169505</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>-0.00040111076828139856 +/- 0.0011793591393777498</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.060783708731872874 +/- 0.006957027818014815</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.018111693921629125 +/- 0.003601019436102377</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.018111693921629125 +/- 0.003601019436102377</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.014686825053995678 +/- 0.0035049606470010193</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.023295279234804057 +/- 0.0037390213447702925</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.02974390620178957 +/- 0.0043178909434213805</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.0374884294970688 +/- 0.003532152790502694</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.03853748842949707 +/- 0.0026522459947968713</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.02162912681271213 +/- 0.004585735447845404</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.2662141314409133 +/- 0.008043311212818587</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.0013884603517432814 +/- 0.002633514700817101</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.11289725393397101 +/- 0.008174392680169505</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-0.0003702560937982158 +/- 0.0011853978841282684</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.01910456915056734 +/- 0.0024341870128753436</t>
+          <t>0.01913523459061641 +/- 0.002492026943135265</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.01726464274762347 +/- 0.0022410961533999977</t>
+          <t>0.017295308187672533 +/- 0.002241725468567566</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.006685065930696133 +/- 0.001849103150160243</t>
+          <t>0.006654400490647061 +/- 0.0018299329957480164</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.020606601248884915 +/- 0.004831514878110414</t>
+          <t>0.020576865893547423 +/- 0.004838372698457696</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.00698780850431161 +/- 0.002330956003243066</t>
+          <t>0.006958073148974109 +/- 0.00230405835596914</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.0013083556348498448 +/- 0.001704020075158405</t>
+          <t>0.0012786202795123437 +/- 0.0016928272765376338</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.006274159976211724 +/- 0.0030103284236734653</t>
+          <t>-0.006244424620874234 +/- 0.003014877634406548</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0004149377593360981 +/- 0.0013333991558034325</t>
+          <t>0.00038529934795494825 +/- 0.001299028275092534</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.12409602845287493 +/- 0.0071490035463822035</t>
+          <t>0.12412566686425608 +/- 0.00717935075362936</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0004191504334241524</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
           <t>-5.927682276229973e-05 +/- 0.0004923902704752842</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0004191504334241524</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.002239709443099236 +/- 0.00147779123677163</t>
+          <t>-0.0022699757869248938 +/- 0.0015026866328458014</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.062257869249394714 +/- 0.0048047284605499735</t>
+          <t>0.06222760290556904 +/- 0.0047551884209425825</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.007808716707021812 +/- 0.0032676439651975224</t>
+          <t>0.007748184019370485 +/- 0.003316064388571988</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.013634925656437813 +/- 0.002809871647679411</t>
+          <t>-0.013603290098070209 +/- 0.002875183237583474</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.00025308446694083386 +/- 0.0007045573379095038</t>
+          <t>-0.0002847200253084381 +/- 0.0006995679970735625</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0005621486570892787 +/- 0.0027961310787756625</t>
+          <t>-0.0005933791380386855 +/- 0.002819232097710156</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.021049344159900108 +/- 0.002435977514053707</t>
+          <t>0.0210181136789507 +/- 0.0024553196765772496</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0005933791380387299 +/- 0.0002946277680217573</t>
+          <t>0.000562148657089323 +/- 0.00030599497099102996</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.0017489069331667827 +/- 0.0011867582760774597</t>
+          <t>0.001717676452217376 +/- 0.001203488374016104</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.00894941634241253 +/- 0.0021643766764191394</t>
+          <t>0.008919485184076703 +/- 0.002174081987109825</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.0008680035917390638 +/- 0.0012730422219776971</t>
+          <t>0.0008979347500748913 +/- 0.0012485276033890986</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-6.0882800608830226e-05 +/- 0.0002982635912064861</t>
+          <t>-3.0441400304415113e-05 +/- 0.0002528652621892961</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
